--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4471" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4509" uniqueCount="699">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T10:00:28+00:00</t>
+    <t>2025-07-07T12:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -704,6 +704,22 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -2497,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP116"/>
+  <dimension ref="A1:AP117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.81640625" customWidth="true" bestFit="true"/>
@@ -5221,7 +5237,7 @@
         <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5307,46 +5323,44 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>114</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5394,7 +5408,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5418,7 +5432,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5436,7 +5450,7 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5449,23 +5463,25 @@
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5514,7 +5530,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5526,22 +5542,22 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5549,14 +5565,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5575,17 +5591,17 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5634,7 +5650,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5649,19 +5665,19 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5669,14 +5685,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5695,18 +5711,18 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5754,7 +5770,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5769,16 +5785,16 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5789,46 +5805,44 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5852,11 +5866,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5874,13 +5890,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5889,19 +5905,19 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5909,10 +5925,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5923,31 +5939,31 @@
         <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5972,35 +5988,35 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AC29" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -6009,19 +6025,19 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -6029,14 +6045,12 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6045,7 +6059,7 @@
         <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>94</v>
@@ -6057,19 +6071,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6097,28 +6111,26 @@
         <v>177</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6142,10 +6154,10 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -6153,24 +6165,26 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -6179,16 +6193,20 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6212,13 +6230,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6236,19 +6254,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>110</v>
+        <v>273</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6260,10 +6278,10 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>111</v>
+        <v>282</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6271,21 +6289,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6297,17 +6315,15 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6344,31 +6360,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6391,46 +6407,44 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6466,19 +6480,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>121</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6490,7 +6504,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6499,10 +6513,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>293</v>
+        <v>111</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6513,10 +6527,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6524,31 +6538,35 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6596,19 +6614,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>110</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6617,10 +6635,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6631,21 +6649,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6657,17 +6675,15 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6704,31 +6720,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6751,52 +6767,50 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>301</v>
+        <v>116</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6826,31 +6840,31 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6859,10 +6873,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>307</v>
+        <v>111</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6873,10 +6887,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6884,13 +6898,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6899,24 +6913,26 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6958,7 +6974,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6979,10 +6995,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6993,10 +7009,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7004,13 +7020,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -7019,24 +7035,24 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>82</v>
@@ -7078,7 +7094,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7099,10 +7115,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7113,10 +7129,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7124,13 +7140,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7139,24 +7155,24 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>82</v>
@@ -7198,7 +7214,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7219,10 +7235,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7233,10 +7249,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7259,19 +7275,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>335</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7320,7 +7334,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7341,10 +7355,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7355,10 +7369,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7381,19 +7395,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7442,7 +7456,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7463,10 +7477,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7477,24 +7491,24 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7503,19 +7517,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>269</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7540,13 +7554,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7564,10 +7578,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>93</v>
@@ -7579,62 +7593,66 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>108</v>
+        <v>359</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7658,13 +7676,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7682,10 +7700,10 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>110</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -7694,44 +7712,44 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>111</v>
+        <v>368</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7743,17 +7761,15 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7790,31 +7806,31 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7837,18 +7853,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>81</v>
@@ -7860,23 +7876,21 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7912,9 +7926,11 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7922,7 +7938,7 @@
         <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>291</v>
+        <v>121</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7934,7 +7950,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7943,10 +7959,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>293</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7957,14 +7973,12 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7973,7 +7987,7 @@
         <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7988,16 +8002,16 @@
         <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8034,19 +8048,17 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8067,10 +8079,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8081,18 +8093,20 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="C47" s="2"/>
+      <c r="C47" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8104,19 +8118,23 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8164,19 +8182,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>110</v>
+        <v>296</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8185,10 +8203,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8199,21 +8217,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8225,17 +8243,15 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8272,31 +8288,31 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8319,21 +8335,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8342,29 +8358,27 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>301</v>
+        <v>116</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8394,31 +8408,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8427,10 +8441,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>307</v>
+        <v>111</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8441,10 +8455,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8452,7 +8466,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8467,24 +8481,26 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8526,7 +8542,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8547,10 +8563,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8561,10 +8577,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8572,7 +8588,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>93</v>
@@ -8587,24 +8603,24 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>82</v>
@@ -8646,7 +8662,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8667,10 +8683,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8681,10 +8697,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8692,7 +8708,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8707,24 +8723,24 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8766,7 +8782,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8787,10 +8803,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8801,10 +8817,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8827,19 +8843,17 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>335</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8888,7 +8902,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8909,10 +8923,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8923,10 +8937,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8949,19 +8963,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>340</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9010,7 +9024,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9031,10 +9045,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9045,10 +9059,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9056,13 +9070,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9071,19 +9085,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>390</v>
+        <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>394</v>
+        <v>353</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9132,7 +9146,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9147,19 +9161,19 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>396</v>
+        <v>355</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>397</v>
+        <v>356</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9167,10 +9181,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9178,13 +9192,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9193,18 +9207,20 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9252,13 +9268,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -9267,19 +9283,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>362</v>
+        <v>401</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9287,21 +9303,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9313,20 +9329,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>411</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9374,13 +9388,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9389,19 +9403,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>413</v>
+        <v>367</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9409,24 +9423,24 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9435,19 +9449,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9496,7 +9510,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9505,25 +9519,25 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>424</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9531,24 +9545,24 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9557,18 +9571,20 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>129</v>
+        <v>423</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9616,7 +9632,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9625,25 +9641,25 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>429</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9651,10 +9667,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9665,7 +9681,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9677,18 +9693,18 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9736,13 +9752,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9751,19 +9767,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9771,10 +9787,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9785,10 +9801,10 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9797,19 +9813,17 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9846,59 +9860,59 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC61" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9919,19 +9933,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9968,19 +9982,17 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9989,7 +10001,7 @@
         <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9998,29 +10010,31 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10032,25 +10046,29 @@
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>107</v>
+        <v>451</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>108</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10098,7 +10116,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10107,47 +10125,47 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -10159,17 +10177,15 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10206,31 +10222,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10253,46 +10269,44 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>465</v>
+        <v>114</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>466</v>
+        <v>115</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>467</v>
+        <v>116</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10328,31 +10342,31 @@
         <v>82</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>470</v>
+        <v>121</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10361,10 +10375,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>472</v>
+        <v>111</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10375,10 +10389,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10386,83 +10400,83 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>470</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q66" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="R66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10483,10 +10497,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10497,10 +10511,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10508,37 +10522,39 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q67" s="2"/>
+      <c r="Q67" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="R67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10558,13 +10574,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10582,7 +10598,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10603,10 +10619,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10617,10 +10633,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10643,24 +10659,24 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>82</v>
@@ -10702,7 +10718,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10711,7 +10727,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10723,10 +10739,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10737,10 +10753,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10763,26 +10779,24 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>82</v>
@@ -10824,7 +10838,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10833,7 +10847,7 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10845,10 +10859,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10859,10 +10873,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10870,7 +10884,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>93</v>
@@ -10882,29 +10896,29 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>82</v>
@@ -10922,13 +10936,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10946,7 +10960,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10955,7 +10969,7 @@
         <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10967,10 +10981,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>196</v>
+        <v>495</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10981,10 +10995,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10998,7 +11012,7 @@
         <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -11007,16 +11021,20 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>108</v>
+        <v>515</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11040,13 +11058,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -11064,7 +11082,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>110</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11073,10 +11091,10 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11085,10 +11103,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>111</v>
+        <v>522</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11099,21 +11117,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11125,17 +11143,15 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11172,31 +11188,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11219,14 +11235,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11242,23 +11258,21 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11294,19 +11308,19 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>291</v>
+        <v>121</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11318,7 +11332,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11327,10 +11341,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>293</v>
+        <v>111</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11341,10 +11355,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11355,7 +11369,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11364,19 +11378,23 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>108</v>
+        <v>292</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11424,19 +11442,19 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>110</v>
+        <v>296</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11445,10 +11463,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>111</v>
+        <v>298</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11459,21 +11477,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11485,17 +11503,15 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11532,31 +11548,31 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11579,21 +11595,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11602,23 +11618,21 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>301</v>
+        <v>116</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11654,31 +11668,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11687,10 +11701,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>307</v>
+        <v>111</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11701,10 +11715,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11712,7 +11726,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>93</v>
@@ -11727,18 +11741,20 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11786,7 +11802,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11807,10 +11823,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11821,10 +11837,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11832,7 +11848,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>93</v>
@@ -11847,18 +11863,18 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11906,7 +11922,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11927,10 +11943,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11941,10 +11957,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11952,7 +11968,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>93</v>
@@ -11967,17 +11983,17 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12026,7 +12042,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12047,10 +12063,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12061,10 +12077,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12087,19 +12103,17 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>335</v>
+        <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12148,7 +12162,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12169,10 +12183,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12183,10 +12197,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12209,19 +12223,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>107</v>
+        <v>340</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12270,7 +12284,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12291,10 +12305,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12305,21 +12319,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12328,22 +12342,22 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>269</v>
+        <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>531</v>
+        <v>350</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>532</v>
+        <v>351</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>533</v>
+        <v>352</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>534</v>
+        <v>353</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12368,11 +12382,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12390,13 +12406,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>529</v>
+        <v>354</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12408,31 +12424,31 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>537</v>
+        <v>355</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>538</v>
+        <v>356</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12451,19 +12467,19 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>541</v>
+        <v>274</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12488,13 +12504,11 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12512,7 +12526,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12530,27 +12544,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12561,7 +12575,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12573,18 +12587,20 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>269</v>
+        <v>546</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12608,11 +12624,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12630,13 +12648,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12648,27 +12666,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12691,15 +12709,17 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>108</v>
+        <v>554</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12724,13 +12744,11 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -12748,7 +12766,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>110</v>
+        <v>553</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12760,44 +12778,44 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>111</v>
+        <v>560</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12809,17 +12827,15 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12856,31 +12872,31 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12903,14 +12919,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12926,23 +12942,21 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12966,29 +12980,31 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>560</v>
+        <v>82</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>291</v>
+        <v>121</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13000,7 +13016,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13009,10 +13025,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>293</v>
+        <v>111</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13023,10 +13039,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13037,7 +13053,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13049,19 +13065,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>345</v>
+        <v>292</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>346</v>
+        <v>293</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>347</v>
+        <v>294</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>348</v>
+        <v>295</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13086,13 +13102,11 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>565</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13110,13 +13124,13 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>349</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
@@ -13131,10 +13145,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>351</v>
+        <v>298</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13145,10 +13159,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13162,28 +13176,28 @@
         <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J89" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I89" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K89" t="s" s="2">
-        <v>269</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>563</v>
+        <v>350</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>564</v>
+        <v>351</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>565</v>
+        <v>352</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>566</v>
+        <v>353</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13208,11 +13222,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y89" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z89" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13230,7 +13246,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>562</v>
+        <v>354</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13251,10 +13267,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>568</v>
+        <v>355</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>569</v>
+        <v>356</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13265,10 +13281,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13282,7 +13298,7 @@
         <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>82</v>
@@ -13291,16 +13307,20 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>108</v>
+        <v>568</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13324,13 +13344,11 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13348,7 +13366,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>110</v>
+        <v>567</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13360,7 +13378,7 @@
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13369,10 +13387,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>111</v>
+        <v>574</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13383,21 +13401,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13409,17 +13427,15 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13456,31 +13472,31 @@
         <v>82</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13503,14 +13519,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13526,23 +13542,21 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13566,29 +13580,31 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>291</v>
+        <v>121</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13600,7 +13616,7 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -13609,10 +13625,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>293</v>
+        <v>111</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13623,10 +13639,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13637,7 +13653,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13649,19 +13665,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>345</v>
+        <v>292</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>346</v>
+        <v>293</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>347</v>
+        <v>294</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>348</v>
+        <v>295</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13686,13 +13702,11 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13710,13 +13724,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>349</v>
+        <v>296</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13731,10 +13745,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>351</v>
+        <v>298</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13745,10 +13759,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13768,21 +13782,23 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>576</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>577</v>
+        <v>350</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>578</v>
+        <v>351</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13830,7 +13846,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>575</v>
+        <v>354</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13848,27 +13864,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>581</v>
+        <v>355</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>582</v>
+        <v>356</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13882,7 +13898,7 @@
         <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13891,16 +13907,16 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13950,7 +13966,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13968,27 +13984,27 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13999,10 +14015,10 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -14011,20 +14027,18 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -14072,45 +14086,45 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>599</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>82</v>
+        <v>597</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14121,7 +14135,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -14133,16 +14147,20 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>107</v>
+        <v>599</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>108</v>
+        <v>600</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14190,19 +14208,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>110</v>
+        <v>598</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14211,10 +14229,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>111</v>
+        <v>606</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14225,21 +14243,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14251,17 +14269,15 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -14310,19 +14326,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14345,14 +14361,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>605</v>
+        <v>113</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14365,26 +14381,24 @@
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>606</v>
+        <v>115</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>607</v>
+        <v>116</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O99" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14432,7 +14446,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>608</v>
+        <v>121</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14456,7 +14470,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14474,26 +14488,26 @@
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>610</v>
+        <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>611</v>
@@ -14501,8 +14515,12 @@
       <c r="M100" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+      <c r="N100" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14550,19 +14568,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>613</v>
+        <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14571,10 +14589,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>615</v>
+        <v>196</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14585,10 +14603,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14611,13 +14629,13 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14668,7 +14686,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14677,7 +14695,7 @@
         <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>105</v>
@@ -14689,10 +14707,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14703,10 +14721,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14729,20 +14747,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>269</v>
+        <v>615</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N102" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="O102" t="s" s="2">
-        <v>624</v>
-      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14766,13 +14780,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>626</v>
+        <v>82</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14790,7 +14804,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14799,7 +14813,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14808,13 +14822,13 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>538</v>
+        <v>624</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14825,10 +14839,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14839,7 +14853,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14851,19 +14865,19 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14888,13 +14902,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14912,13 +14926,13 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
@@ -14930,13 +14944,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14947,10 +14961,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14961,7 +14975,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14973,17 +14987,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15008,13 +15024,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>640</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15032,13 +15048,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -15050,13 +15066,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>632</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>641</v>
+        <v>543</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15067,10 +15083,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15093,7 +15109,7 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>107</v>
+        <v>642</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>643</v>
@@ -15102,7 +15118,9 @@
         <v>644</v>
       </c>
       <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15150,7 +15168,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15171,10 +15189,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15185,10 +15203,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15199,7 +15217,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15208,10 +15226,10 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>647</v>
+        <v>107</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>648</v>
@@ -15219,9 +15237,7 @@
       <c r="M106" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="N106" t="s" s="2">
-        <v>650</v>
-      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15270,13 +15286,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
@@ -15291,10 +15307,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>651</v>
+        <v>619</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15305,10 +15321,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15331,16 +15347,16 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15390,7 +15406,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15411,10 +15427,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15425,10 +15441,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15442,7 +15458,7 @@
         <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>82</v>
@@ -15451,20 +15467,18 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>594</v>
+        <v>659</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>660</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O108" t="s" s="2">
         <v>662</v>
       </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15512,7 +15526,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15524,19 +15538,19 @@
         <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15547,10 +15561,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15561,28 +15575,32 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>107</v>
+        <v>599</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>108</v>
+        <v>665</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15630,19 +15648,19 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>110</v>
+        <v>664</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>82</v>
+        <v>668</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15651,10 +15669,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>111</v>
+        <v>670</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15665,21 +15683,21 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15691,17 +15709,15 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15750,19 +15766,19 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15785,14 +15801,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>605</v>
+        <v>113</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15805,26 +15821,24 @@
         <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>606</v>
+        <v>115</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>607</v>
+        <v>116</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O111" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15872,7 +15886,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>608</v>
+        <v>121</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15896,7 +15910,7 @@
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15907,45 +15921,45 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>269</v>
+        <v>114</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>670</v>
+        <v>611</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>671</v>
+        <v>612</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>672</v>
+        <v>117</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>673</v>
+        <v>232</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -15970,13 +15984,13 @@
         <v>82</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15994,34 +16008,34 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>669</v>
+        <v>613</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>674</v>
+        <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>363</v>
+        <v>196</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>82</v>
@@ -16029,10 +16043,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16040,7 +16054,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>93</v>
@@ -16055,19 +16069,19 @@
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16095,10 +16109,10 @@
         <v>155</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>680</v>
+        <v>363</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>681</v>
+        <v>364</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16116,16 +16130,16 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>682</v>
+        <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>105</v>
@@ -16134,27 +16148,27 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>454</v>
+        <v>367</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>455</v>
+        <v>368</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16174,22 +16188,22 @@
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>269</v>
+        <v>681</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>513</v>
+        <v>454</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16217,10 +16231,10 @@
         <v>155</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>514</v>
+        <v>685</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>515</v>
+        <v>686</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16238,7 +16252,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16247,7 +16261,7 @@
         <v>93</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>105</v>
@@ -16256,19 +16270,19 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>82</v>
+        <v>688</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>196</v>
+        <v>459</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>517</v>
+        <v>460</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
     </row>
     <row r="115" hidden="true">
@@ -16280,17 +16294,17 @@
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>82</v>
@@ -16299,19 +16313,19 @@
         <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>531</v>
+        <v>690</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>532</v>
+        <v>691</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>533</v>
+        <v>692</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16339,10 +16353,10 @@
         <v>155</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>690</v>
+        <v>519</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16366,10 +16380,10 @@
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>82</v>
+        <v>693</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>105</v>
@@ -16378,31 +16392,31 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>537</v>
+        <v>196</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -16421,19 +16435,19 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>692</v>
+        <v>536</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>693</v>
+        <v>537</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>597</v>
+        <v>538</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>598</v>
+        <v>539</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16458,13 +16472,13 @@
         <v>82</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>82</v>
+        <v>695</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16482,7 +16496,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16500,23 +16514,145 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>600</v>
+        <v>542</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>601</v>
+        <v>543</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP116" t="s" s="2">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="P117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP117" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP116">
+  <autoFilter ref="A1:AP117">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16526,7 +16662,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI115">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1393,7 +1393,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2526,7 +2526,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
